--- a/outputs/marketing/auditoria/Personas_Estado_Civil.xlsx
+++ b/outputs/marketing/auditoria/Personas_Estado_Civil.xlsx
@@ -27700,10 +27700,10 @@
         </is>
       </c>
       <c r="K356" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L356" s="2" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="M356" s="2" t="inlineStr">
         <is>
@@ -35376,10 +35376,10 @@
         </is>
       </c>
       <c r="K457" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L457" s="3" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="M457" s="3" t="inlineStr">
         <is>
@@ -45940,10 +45940,10 @@
         </is>
       </c>
       <c r="K596" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L596" s="2" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="M596" s="2" t="inlineStr">
         <is>
@@ -46092,10 +46092,10 @@
         </is>
       </c>
       <c r="K598" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L598" s="2" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="M598" s="2" t="inlineStr">
         <is>
